--- a/Ref_Files/Test_Excell.xlsx
+++ b/Ref_Files/Test_Excell.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" state="visible" r:id="rId3"/>
@@ -1169,7 +1169,10 @@
         <v>200</v>
       </c>
       <c r="F14" s="20"/>
-      <c r="G14" s="21"/>
+      <c r="G14" s="21" t="n">
+        <f aca="false">E14*F14</f>
+        <v>0</v>
+      </c>
       <c r="H14" s="14"/>
     </row>
     <row r="15" customFormat="false" ht="17.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2924,7 +2927,10 @@
         <v>200</v>
       </c>
       <c r="F11" s="20"/>
-      <c r="G11" s="21"/>
+      <c r="G11" s="21" t="n">
+        <f aca="false">E11*F11</f>
+        <v>0</v>
+      </c>
       <c r="H11" s="14"/>
     </row>
     <row r="12" customFormat="false" ht="17.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3555,7 +3561,10 @@
         <v>200</v>
       </c>
       <c r="F12" s="20"/>
-      <c r="G12" s="21"/>
+      <c r="G12" s="21" t="n">
+        <f aca="false">E12*F12</f>
+        <v>0</v>
+      </c>
       <c r="H12" s="14"/>
     </row>
     <row r="13" customFormat="false" ht="17.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
